--- a/90606_REPORT_BOTTEGA_09-01-2026.xlsx
+++ b/90606_REPORT_BOTTEGA_09-01-2026.xlsx
@@ -9,13 +9,12 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
-    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="70">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -50,39 +49,6 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
-    <t>16:00 - 16:59</t>
-  </si>
-  <si>
-    <t>17:00 - 17:59</t>
-  </si>
-  <si>
-    <t>18:00 - 18:59</t>
-  </si>
-  <si>
-    <t>19:00 - 19:59</t>
-  </si>
-  <si>
-    <t>20:00 - 20:59</t>
-  </si>
-  <si>
-    <t>21:00 - 21:59</t>
-  </si>
-  <si>
-    <t>22:00 - 22:59</t>
-  </si>
-  <si>
-    <t>23:00 - 23:59</t>
-  </si>
-  <si>
-    <t>0:00 - 0:59</t>
-  </si>
-  <si>
-    <t>1:00 - 1:59</t>
-  </si>
-  <si>
-    <t>2:00 - 2:59</t>
-  </si>
-  <si>
     <t>TOTALE INCASSI 09/01/2026</t>
   </si>
   <si>
@@ -113,40 +79,64 @@
     <t>Bistecca Con Filetto 30-40 G</t>
   </si>
   <si>
+    <t>610005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bistecca Con Filetto </t>
+  </si>
+  <si>
     <t>610001</t>
   </si>
   <si>
     <t>Bistecca In Costata</t>
   </si>
   <si>
+    <t>50-004-011-002120</t>
+  </si>
+  <si>
+    <t>Controfiletto B.A.</t>
+  </si>
+  <si>
+    <t>50-004-011-000730</t>
+  </si>
+  <si>
+    <t>Stinco Di Suino (Con Patate)</t>
+  </si>
+  <si>
+    <t>50-004-011-000750</t>
+  </si>
+  <si>
+    <t>Punta Di Petto (Con Patate)</t>
+  </si>
+  <si>
+    <t>50-004-011-000860</t>
+  </si>
+  <si>
+    <t>Patate Al Forno</t>
+  </si>
+  <si>
+    <t>50-004-011-001680</t>
+  </si>
+  <si>
+    <t>Verdure</t>
+  </si>
+  <si>
     <t>50-004-011-000560</t>
   </si>
   <si>
     <t>Arrosticini Di Pecora</t>
   </si>
   <si>
-    <t>50-004-011-000860</t>
-  </si>
-  <si>
-    <t>Patate Al Forno</t>
-  </si>
-  <si>
-    <t>610005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bistecca Con Filetto </t>
-  </si>
-  <si>
-    <t>50-004-011-002120</t>
-  </si>
-  <si>
-    <t>Controfiletto B.A.</t>
-  </si>
-  <si>
-    <t>50-004-011-000750</t>
-  </si>
-  <si>
-    <t>Punta Di Petto (Con Patate)</t>
+    <t>50-004-011-000600</t>
+  </si>
+  <si>
+    <t>Grigliata Mista</t>
+  </si>
+  <si>
+    <t>50-004-011-002270</t>
+  </si>
+  <si>
+    <t>Cosce Di Pollo</t>
   </si>
   <si>
     <t>50-004-011-000590</t>
@@ -155,16 +145,10 @@
     <t xml:space="preserve">Filetto B.A. </t>
   </si>
   <si>
-    <t>50-004-011-000730</t>
-  </si>
-  <si>
-    <t>Stinco Di Suino (Con Patate)</t>
-  </si>
-  <si>
-    <t>50-004-011-001680</t>
-  </si>
-  <si>
-    <t>Verdure</t>
+    <t>50-004-011-000610</t>
+  </si>
+  <si>
+    <t>Grigliata Mista Xxl</t>
   </si>
   <si>
     <t>50-004-011-001300</t>
@@ -173,66 +157,36 @@
     <t>Costine di suino</t>
   </si>
   <si>
-    <t>50-004-011-000600</t>
-  </si>
-  <si>
-    <t>Grigliata Mista</t>
-  </si>
-  <si>
-    <t>50-004-011-002270</t>
-  </si>
-  <si>
-    <t>Cosce Di Pollo</t>
-  </si>
-  <si>
-    <t>50-004-011-000610</t>
-  </si>
-  <si>
-    <t>Grigliata Mista Xxl</t>
-  </si>
-  <si>
     <t>610049</t>
   </si>
   <si>
     <t>Fiorentina Con Filetto (Asporto)</t>
   </si>
   <si>
+    <t>50-004-011-002280</t>
+  </si>
+  <si>
+    <t>Alette Di Pollo</t>
+  </si>
+  <si>
+    <t>50-004-011-000700</t>
+  </si>
+  <si>
+    <t>Tagliata Pollo</t>
+  </si>
+  <si>
     <t>50-004-011-002070</t>
   </si>
   <si>
     <t>Hamburger bovino adulto (con patate)</t>
   </si>
   <si>
-    <t>50-004-011-002280</t>
-  </si>
-  <si>
-    <t>Alette Di Pollo</t>
-  </si>
-  <si>
-    <t>50-004-011-000700</t>
-  </si>
-  <si>
-    <t>Tagliata Pollo</t>
-  </si>
-  <si>
     <t>50-004-011-002230</t>
   </si>
   <si>
     <t>Pollo Alla Cacciatora Con Contorno</t>
   </si>
   <si>
-    <t>50-004-011-002170</t>
-  </si>
-  <si>
-    <t>Tomahawk Suino (Con Patate)</t>
-  </si>
-  <si>
-    <t>610003</t>
-  </si>
-  <si>
-    <t>Bistecca Costata 30-40 G</t>
-  </si>
-  <si>
     <t>50-004-011-000660</t>
   </si>
   <si>
@@ -251,12 +205,6 @@
     <t>Caesar Salad</t>
   </si>
   <si>
-    <t>50-004-011-000650</t>
-  </si>
-  <si>
-    <t>Mezzo Pollo Ruspante</t>
-  </si>
-  <si>
     <t>50-004-011-002190</t>
   </si>
   <si>
@@ -276,21 +224,6 @@
   </si>
   <si>
     <t>12:00-15:59</t>
-  </si>
-  <si>
-    <t>16:00-18:59</t>
-  </si>
-  <si>
-    <t>19:00-02:59</t>
-  </si>
-  <si>
-    <t>09/01/2026</t>
-  </si>
-  <si>
-    <t>VAR %</t>
-  </si>
-  <si>
-    <t>02/01/2026</t>
   </si>
 </sst>
 </file>
@@ -428,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -441,27 +374,13 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -549,115 +468,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="2">
+      <c r="A11" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="5">
-        <v>188.3637</v>
+      <c r="B11" t="n" s="1">
+        <v>2599.27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="4">
+      <c r="A12" t="s" s="1">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="7">
-        <v>89.7272</v>
+      <c r="B12" t="n" s="1">
+        <v>4354.55</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="2">
+      <c r="A13" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="5">
-        <v>49.2727</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="4">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n" s="7">
-        <v>195.5454</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n" s="5">
-        <v>280.1819</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="4">
-        <v>16</v>
-      </c>
-      <c r="B16" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B17" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="4">
-        <v>18</v>
-      </c>
-      <c r="B18" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="4">
-        <v>20</v>
-      </c>
-      <c r="B20" t="n" s="7">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B21" t="n" s="5">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="1">
-        <v>22</v>
-      </c>
-      <c r="B22" t="n" s="1">
-        <v>3402.36</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s" s="1">
-        <v>23</v>
-      </c>
-      <c r="B23" t="n" s="1">
-        <v>7623.73</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s" s="1">
-        <v>24</v>
-      </c>
-      <c r="B24" t="n" s="1">
-        <v>-55.37</v>
+      <c r="B13" t="n" s="1">
+        <v>-40.31</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -679,265 +510,265 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>583.909</v>
+        <v>356.9999</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>10.04</v>
+        <v>6.14</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>17.16</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>312.2728</v>
+        <v>197.3637</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>6.87</v>
+        <v>3.87</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>9.18</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>209.1727</v>
+        <v>189.5455</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>157.0</v>
+        <v>4.17</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>6.15</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>200.7271</v>
+        <v>171.8181</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>37.0</v>
+        <v>9.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>5.9</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>197.3637</v>
+        <v>166.2636</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>3.87</v>
+        <v>12.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>190.909</v>
+        <v>159.4636</v>
       </c>
       <c r="D7" t="n" s="5">
         <v>10.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>5.61</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>175.7363</v>
+        <v>158.1817</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>11.0</v>
+        <v>29.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>5.17</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>167.2728</v>
+        <v>152.7273</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>8.0</v>
+        <v>24.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>4.92</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>166.2636</v>
+        <v>127.9091</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>12.0</v>
+        <v>96.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>164.1818</v>
+        <v>127.6363</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>26.0</v>
+        <v>8.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>4.83</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>146.282</v>
+        <v>108.0</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>4.3</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>127.6363</v>
+        <v>104.5455</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>3.75</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>113.3727</v>
+        <v>98.1819</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>3.33</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>98.1819</v>
+        <v>94.8183</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>2.89</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>90.9091</v>
@@ -946,208 +777,157 @@
         <v>2.0</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>88.4547</v>
+        <v>81.0</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>2.6</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>81.0</v>
+        <v>70.3635</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>2.38</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>70.3635</v>
+        <v>50.5456</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>63.1819</v>
+        <v>37.9091</v>
       </c>
       <c r="D20" t="n" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E20" t="n" s="7">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C21" t="n" s="5">
-        <v>50.9</v>
+        <v>25.2727</v>
       </c>
       <c r="D21" t="n" s="5">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E21" t="n" s="5">
-        <v>1.5</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C22" t="n" s="7">
-        <v>39.2727</v>
+        <v>12.6364</v>
       </c>
       <c r="D22" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E22" t="n" s="7">
-        <v>1.15</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C23" t="n" s="5">
-        <v>25.2727</v>
+        <v>11.7273</v>
       </c>
       <c r="D23" t="n" s="5">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E23" t="n" s="5">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C24" t="n" s="7">
-        <v>12.6364</v>
+        <v>5.4545</v>
       </c>
       <c r="D24" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E24" t="n" s="7">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="C25" t="n" s="5">
-        <v>11.7273</v>
-      </c>
-      <c r="D25" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E25" t="n" s="5">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="4">
-        <v>78</v>
-      </c>
-      <c r="B26" t="s" s="4">
-        <v>79</v>
-      </c>
-      <c r="C26" t="n" s="7">
-        <v>9.9091</v>
-      </c>
-      <c r="D26" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="E26" t="n" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="C27" t="n" s="5">
-        <v>5.4545</v>
-      </c>
-      <c r="D27" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E27" t="n" s="5">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="1">
-        <v>82</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" t="n" s="1">
-        <v>3402.36</v>
-      </c>
-      <c r="D28" t="n" s="1">
-        <v>356.78</v>
-      </c>
-      <c r="E28" t="n" s="1">
+      <c r="A25" t="s" s="1">
+        <v>65</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="n" s="1">
+        <v>2599.27</v>
+      </c>
+      <c r="D25" t="n" s="1">
+        <v>259.18</v>
+      </c>
+      <c r="E25" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -1158,7 +938,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -1169,13 +949,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1183,15 +963,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>2.0</v>
@@ -1202,10 +982,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>1.0</v>
@@ -1216,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n" s="1">
         <v>3.0</v>
@@ -1231,15 +1011,15 @@
     <row r="6"/>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" t="n" s="7">
         <v>96.0</v>
@@ -1250,10 +1030,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n" s="5">
         <v>28.0</v>
@@ -1264,10 +1044,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>24.0</v>
@@ -1278,10 +1058,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>12.0</v>
@@ -1292,10 +1072,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>12.0</v>
@@ -1306,10 +1086,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>10.0</v>
@@ -1320,10 +1100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>9.0</v>
@@ -1334,10 +1114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>8.0</v>
@@ -1348,10 +1128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>7.0</v>
@@ -1362,10 +1142,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>7.0</v>
@@ -1376,10 +1156,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>6.14</v>
@@ -1390,10 +1170,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>6.0</v>
@@ -1404,10 +1184,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>5.0</v>
@@ -1418,10 +1198,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>4.17</v>
@@ -1432,10 +1212,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>4.0</v>
@@ -1446,10 +1226,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>4.0</v>
@@ -1460,10 +1240,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>3.87</v>
@@ -1474,10 +1254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>3.0</v>
@@ -1488,10 +1268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>2.0</v>
@@ -1502,10 +1282,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>2.0</v>
@@ -1516,10 +1296,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>1.0</v>
@@ -1530,10 +1310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>1.0</v>
@@ -1544,10 +1324,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>1.0</v>
@@ -1558,10 +1338,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="1">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C31" t="n" s="1">
         <v>256.18</v>
@@ -1571,389 +1351,13 @@
       </c>
     </row>
     <row r="32"/>
-    <row r="33">
-      <c r="A33" t="s" s="1">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="4">
-        <v>34</v>
-      </c>
-      <c r="B34" t="s" s="4">
-        <v>35</v>
-      </c>
-      <c r="C34" t="n" s="7">
-        <v>45.0</v>
-      </c>
-      <c r="D34" t="n" s="7">
-        <v>61.3636</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="C35" t="n" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="D35" t="n" s="5">
-        <v>31.6363</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="4">
-        <v>50</v>
-      </c>
-      <c r="B36" t="s" s="4">
-        <v>51</v>
-      </c>
-      <c r="C36" t="n" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="D36" t="n" s="7">
-        <v>40.6364</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C37" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D37" t="n" s="5">
-        <v>25.2727</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C38" t="n" s="7">
-        <v>1.9</v>
-      </c>
-      <c r="D38" t="n" s="7">
-        <v>110.5455</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="C39" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D39" t="n" s="5">
-        <v>19.0909</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="4">
-        <v>42</v>
-      </c>
-      <c r="B40" t="s" s="4">
-        <v>43</v>
-      </c>
-      <c r="C40" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D40" t="n" s="7">
-        <v>16.2727</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C41" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D41" t="n" s="5">
-        <v>12.6364</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="4">
-        <v>78</v>
-      </c>
-      <c r="B42" t="s" s="4">
-        <v>79</v>
-      </c>
-      <c r="C42" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D42" t="n" s="7">
-        <v>9.9091</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="1">
-        <v>84</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="C43" t="n" s="1">
-        <v>61.9</v>
-      </c>
-      <c r="D43" t="n" s="1">
-        <v>327.36</v>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" t="s" s="1">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="4">
-        <v>34</v>
-      </c>
-      <c r="B46" t="s" s="4">
-        <v>35</v>
-      </c>
-      <c r="C46" t="n" s="7">
-        <v>16.0</v>
-      </c>
-      <c r="D46" t="n" s="7">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C47" t="n" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D47" t="n" s="5">
-        <v>62.7273</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="4">
-        <v>68</v>
-      </c>
-      <c r="B48" t="s" s="4">
-        <v>69</v>
-      </c>
-      <c r="C48" t="n" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="D48" t="n" s="7">
-        <v>50.9</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="C49" t="n" s="5">
-        <v>2.7</v>
-      </c>
-      <c r="D49" t="n" s="5">
-        <v>122.7273</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s" s="4">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s" s="4">
-        <v>31</v>
-      </c>
-      <c r="C50" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D50" t="n" s="7">
-        <v>116.3636</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C51" t="n" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D51" t="n" s="5">
-        <v>11.4545</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="4">
-        <v>36</v>
-      </c>
-      <c r="B52" t="s" s="4">
-        <v>37</v>
-      </c>
-      <c r="C52" t="n" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D52" t="n" s="7">
-        <v>10.9091</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="C53" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D53" t="n" s="5">
-        <v>39.2727</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s" s="4">
-        <v>66</v>
-      </c>
-      <c r="B54" t="s" s="4">
-        <v>67</v>
-      </c>
-      <c r="C54" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D54" t="n" s="7">
-        <v>12.6364</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C55" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D55" t="n" s="5">
-        <v>12.6364</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s" s="4">
-        <v>50</v>
-      </c>
-      <c r="B56" t="s" s="4">
-        <v>51</v>
-      </c>
-      <c r="C56" t="n" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="D56" t="n" s="7">
-        <v>10.8273</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C57" t="n" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D57" t="n" s="5">
-        <v>5.3727</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="1">
-        <v>84</v>
-      </c>
-      <c r="B58" t="s" s="4">
-        <v>85</v>
-      </c>
-      <c r="C58" t="n" s="1">
-        <v>35.7</v>
-      </c>
-      <c r="D58" t="n" s="1">
-        <v>475.73</v>
-      </c>
-    </row>
-    <row r="59"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>89</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>90</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="B2" s="12" t="n">
-        <f>(A2-C2)/C2</f>
-        <v>0.0</v>
-      </c>
-      <c r="C2" t="n" s="9">
-        <v>0.0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>